--- a/ConfigExporter/xlsx/chess_board.xlsx
+++ b/ConfigExporter/xlsx/chess_board.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Project\WeiqiXN\ConfigExporter\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F7B5D55-367F-453A-B36A-356DE174BBEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15FF1152-B3C2-4A9D-A09E-744CC36E1CD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5925" yWindow="3060" windowWidth="29205" windowHeight="13680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5580" yWindow="2715" windowWidth="13425" windowHeight="13680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chess_board" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -76,6 +76,18 @@
   </si>
   <si>
     <t>19x19</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>相机y轴额外偏移</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vcamYOffset</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -438,15 +450,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.625" style="1" customWidth="1"/>
     <col min="2" max="2" width="17.25" style="1" customWidth="1"/>
-    <col min="3" max="3" width="23.625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="23.625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -456,8 +468,11 @@
       <c r="C1" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D1" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -467,8 +482,11 @@
       <c r="C2" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D2" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
@@ -478,8 +496,11 @@
       <c r="C3" s="4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="D3" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>2</v>
       </c>
@@ -489,8 +510,11 @@
       <c r="C4" s="5" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D4" s="5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>10</v>
       </c>
@@ -498,8 +522,11 @@
       <c r="C5" s="4">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D5" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>11</v>
       </c>
@@ -507,14 +534,20 @@
       <c r="C6" s="4">
         <v>13</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D6" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>12</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4">
         <v>19</v>
+      </c>
+      <c r="D7" s="4">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/ConfigExporter/xlsx/chess_board.xlsx
+++ b/ConfigExporter/xlsx/chess_board.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Project\WeiqiXN\ConfigExporter\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15FF1152-B3C2-4A9D-A09E-744CC36E1CD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F988DD0-7468-4A8B-92A7-7F38E6C1CB3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5580" yWindow="2715" windowWidth="13425" windowHeight="13680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -523,7 +523,7 @@
         <v>9</v>
       </c>
       <c r="D5" s="4">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -535,7 +535,7 @@
         <v>13</v>
       </c>
       <c r="D6" s="4">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -547,7 +547,7 @@
         <v>19</v>
       </c>
       <c r="D7" s="4">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
